--- a/assets/documents/Walk Though Scenarios.xlsx
+++ b/assets/documents/Walk Though Scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29301"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ZEZ000\WORK\Scrap\Training _ Walkthrough Matrials\client_site_updated\assets\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{7D39C2A3-284B-4795-A933-DCBD14EFC339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{670F30F2-2D55-4E74-AFC4-BAC3DB3809F9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510F3263-5C32-46C2-ACBE-E0E7E5B49889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93F6A266-42A5-4368-AEE9-9E1E32234030}"/>
+    <workbookView xWindow="-16320" yWindow="-9270" windowWidth="16440" windowHeight="28320" xr2:uid="{93F6A266-42A5-4368-AEE9-9E1E32234030}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t>Task</t>
   </si>
@@ -44,18 +42,12 @@
     <t>Activity</t>
   </si>
   <si>
-    <t>Owner</t>
-  </si>
-  <si>
     <t>User</t>
   </si>
   <si>
     <t>Login with Admin user</t>
   </si>
   <si>
-    <t>Giza</t>
-  </si>
-  <si>
     <t>Admin</t>
   </si>
   <si>
@@ -65,9 +57,6 @@
     <t>Create Supplier</t>
   </si>
   <si>
-    <t>Supplier Activation Process</t>
-  </si>
-  <si>
     <t>Supplier</t>
   </si>
   <si>
@@ -81,9 +70,6 @@
   </si>
   <si>
     <t xml:space="preserve">View admin Confiquration </t>
-  </si>
-  <si>
-    <t>Jeddah</t>
   </si>
   <si>
     <t xml:space="preserve">Driver make new visit requst </t>
@@ -120,7 +106,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,8 +114,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -138,13 +132,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,71 +323,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -736,282 +695,208 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDF7B12E-DEB8-4892-AC21-22BDA9D3C44F}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="20">
+      <c r="C2" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="22" t="s">
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>5</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="B13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="B15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="B17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="11"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="12"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="7">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="7">
-        <v>2</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="7">
-        <v>3</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="7">
-        <v>4</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="7">
-        <v>5</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="7">
-        <v>6</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="7">
-        <v>7</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="7">
-        <v>8</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="7">
-        <v>9</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="7">
-        <v>10</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="7">
-        <v>11</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="13">
-        <v>12</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>6</v>
+      <c r="C18" s="6" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
